--- a/data/raw/inventory/Week 36/White_Mulberry/Imports (OrderPilot).xlsx
+++ b/data/raw/inventory/Week 36/White_Mulberry/Imports (OrderPilot).xlsx
@@ -2140,7 +2140,7 @@
         <v>216</v>
       </c>
       <c r="E43">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F43" t="s">
         <v>259</v>
@@ -2255,7 +2255,7 @@
         <v>221</v>
       </c>
       <c r="E48">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F48" t="s">
         <v>259</v>
@@ -4072,7 +4072,7 @@
         <v>216</v>
       </c>
       <c r="E127">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F127" t="s">
         <v>260</v>
@@ -4164,7 +4164,7 @@
         <v>220</v>
       </c>
       <c r="E131">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F131" t="s">
         <v>260</v>
@@ -4187,7 +4187,7 @@
         <v>221</v>
       </c>
       <c r="E132">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F132" t="s">
         <v>260</v>
